--- a/para/Cap/Elco.xlsx
+++ b/para/Cap/Elco.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/PyPowerSim/para/Cap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="358" documentId="11_AD4DB114E441178AC67DF439BED5CE16693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5740DB46-A7E6-4FD6-8E50-9C132AA40AEF}"/>
+  <xr:revisionPtr revIDLastSave="362" documentId="11_AD4DB114E441178AC67DF439BED5CE16693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFDFA431-5730-55B2-9FFA-E3F70EA887D8}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1248" yWindow="2844" windowWidth="23040" windowHeight="12204" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18120" yWindow="-2550" windowWidth="18240" windowHeight="28320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="1" r:id="rId1"/>
@@ -722,6 +722,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -729,15 +738,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2098,6 +2098,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2105,7 +2106,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3480,6 +3480,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3487,7 +3488,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4862,6 +4862,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4869,7 +4870,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6244,6 +6244,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6251,7 +6252,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6805,6 +6805,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6812,7 +6813,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6917,7 +6917,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-DE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7366,6 +7366,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7373,7 +7374,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10978,10 +10978,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -11923,36 +11919,36 @@
     </row>
     <row r="29" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="38"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="41"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="41"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="38"/>
     </row>
     <row r="32" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="24"/>
@@ -12175,36 +12171,36 @@
     </row>
     <row r="49" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="37"/>
-      <c r="J50" s="37"/>
-      <c r="K50" s="38"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="41"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B51" s="39" t="s">
+      <c r="B51" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="41"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="37"/>
+      <c r="I51" s="37"/>
+      <c r="J51" s="37"/>
+      <c r="K51" s="38"/>
     </row>
     <row r="52" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="24"/>
@@ -12427,36 +12423,36 @@
     </row>
     <row r="69" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="36" t="s">
+      <c r="A70" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B70" s="37"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
-      <c r="J70" s="37"/>
-      <c r="K70" s="38"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="41"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B71" s="39" t="s">
+      <c r="B71" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C71" s="40"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40"/>
-      <c r="J71" s="40"/>
-      <c r="K71" s="41"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="37"/>
+      <c r="I71" s="37"/>
+      <c r="J71" s="37"/>
+      <c r="K71" s="38"/>
     </row>
     <row r="72" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="24"/>
@@ -12679,36 +12675,36 @@
     </row>
     <row r="89" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" s="36" t="s">
+      <c r="A90" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="B90" s="37"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="37"/>
-      <c r="H90" s="37"/>
-      <c r="I90" s="37"/>
-      <c r="J90" s="37"/>
-      <c r="K90" s="38"/>
+      <c r="B90" s="40"/>
+      <c r="C90" s="40"/>
+      <c r="D90" s="40"/>
+      <c r="E90" s="40"/>
+      <c r="F90" s="40"/>
+      <c r="G90" s="40"/>
+      <c r="H90" s="40"/>
+      <c r="I90" s="40"/>
+      <c r="J90" s="40"/>
+      <c r="K90" s="41"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B91" s="39" t="s">
+      <c r="B91" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C91" s="40"/>
-      <c r="D91" s="40"/>
-      <c r="E91" s="40"/>
-      <c r="F91" s="40"/>
-      <c r="G91" s="40"/>
-      <c r="H91" s="40"/>
-      <c r="I91" s="40"/>
-      <c r="J91" s="40"/>
-      <c r="K91" s="41"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="37"/>
+      <c r="G91" s="37"/>
+      <c r="H91" s="37"/>
+      <c r="I91" s="37"/>
+      <c r="J91" s="37"/>
+      <c r="K91" s="38"/>
     </row>
     <row r="92" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="24"/>
